--- a/data/trans_orig/P80_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P80_2023-Estudios-trans_orig.xlsx
@@ -725,17 +725,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>496194</t>
+          <t>557478</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>485260</t>
+          <t>546808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>503308</t>
+          <t>565734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>748322</t>
+          <t>814161</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>743843</t>
+          <t>809258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>751052</t>
+          <t>817215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1244516</t>
+          <t>1371640</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1233277</t>
+          <t>1359826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1253273</t>
+          <t>1380355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21107</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>366</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>753597</t>
+          <t>819942</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>753597</t>
+          <t>819942</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>753597</t>
+          <t>819942</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1268535</t>
+          <t>1398471</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1268535</t>
+          <t>1398471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1268535</t>
+          <t>1398471</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2249988</t>
+          <t>2180035</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2231137</t>
+          <t>2160270</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2266258</t>
+          <t>2196150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2200238</t>
+          <t>2127618</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2185883</t>
+          <t>2112638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2211808</t>
+          <t>2138779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4450225</t>
+          <t>4307653</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4424588</t>
+          <t>4281079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4469808</t>
+          <t>4328470</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>24170</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40795</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17731</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>30306</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>22704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51253</t>
+          <t>52934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11509</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22486</t>
+          <t>30656</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>22291</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>18936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>45654</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2288721</t>
+          <t>2228843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2288721</t>
+          <t>2228843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2288721</t>
+          <t>2228843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2233863</t>
+          <t>2166984</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2233863</t>
+          <t>2166984</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2233863</t>
+          <t>2166984</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4522583</t>
+          <t>4395827</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4522583</t>
+          <t>4395827</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4522583</t>
+          <t>4395827</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>637681</t>
+          <t>701255</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>628701</t>
+          <t>693469</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>641998</t>
+          <t>705867</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>649521</t>
+          <t>724143</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>642006</t>
+          <t>717473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>654022</t>
+          <t>728870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1287201</t>
+          <t>1425397</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1277042</t>
+          <t>1416430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1293739</t>
+          <t>1432773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16212</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,49 +2325,49 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5262</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5785</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645617</t>
+          <t>710468</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645617</t>
+          <t>710468</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645617</t>
+          <t>710468</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>659769</t>
+          <t>734122</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>659769</t>
+          <t>734122</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>659769</t>
+          <t>734122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1305386</t>
+          <t>1444589</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1305386</t>
+          <t>1444589</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1305386</t>
+          <t>1444589</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3383862</t>
+          <t>3438768</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3361882</t>
+          <t>3412643</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3403717</t>
+          <t>3458196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3598080</t>
+          <t>3665922</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3580711</t>
+          <t>3647083</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3611445</t>
+          <t>3677800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6981942</t>
+          <t>7104690</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6953066</t>
+          <t>7074225</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7005567</t>
+          <t>7129709</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55821</t>
+          <t>62549</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>28273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>61038</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38693</t>
+          <t>44598</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74660</t>
+          <t>85760</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29287</t>
+          <t>38603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>27101</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>56317</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28949</t>
+          <t>30954</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3449276</t>
+          <t>3517840</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3449276</t>
+          <t>3517840</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3449276</t>
+          <t>3517840</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3647228</t>
+          <t>3721047</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3647228</t>
+          <t>3721047</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3647228</t>
+          <t>3721047</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7096504</t>
+          <t>7238887</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7096504</t>
+          <t>7238887</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7096504</t>
+          <t>7238887</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
